--- a/matome.xlsx
+++ b/matome.xlsx
@@ -13,7 +13,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="④_水質管理知識" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑤_廃棄物管理知識" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑥_過去問テーマ検索表(16年560問)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑦_出題基準値・数値ルール一覧" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,29 +71,8 @@
       <color rgb="00002060"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001F497D"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -137,20 +115,8 @@
         <bgColor rgb="00EDF2F8"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F497D"/>
-        <bgColor rgb="001F497D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -186,25 +152,11 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top style="medium">
-        <color rgb="001F497D"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="001F497D"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -241,36 +193,6 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -636,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E20"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -646,6 +568,7 @@
     <col width="54" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -660,6 +583,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -760,7 +684,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>BOD/COD/SS/DO/TOC、活性汚泥法、A2O/MBR、浄化槽法、環境基準・水質汚濁防止法</t>
+          <t>BOD/\(\text{CO}\)D/SS/DO/TOC、活性汚泥法、A2O/MBR、浄化槽法、環境基準・水質汚濁防止法</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -809,6 +733,8 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -880,7 +806,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>CO2 1000ppm、BOD除去率 90% 以上などの法令・計算数値</t>
+          <t>\(\text{\(\text{CO}\)}_2\) 1000ppm、BOD除去率 90% 以上などの法令・計算数値</t>
         </is>
       </c>
     </row>
@@ -912,7 +838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -925,6 +851,7 @@
     <col width="55" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -939,6 +866,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
         <is>
@@ -989,11 +917,11 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>・熱抵抗: R = d / λ  [m²・K/W]
-・総合熱貫流抵抗: R_total = R_i + Σ(d_k / λ_k) + R_o + R_air
-・熱貫流率(熱通過率): U = 1 / R_total  [W/(m²・K)]
-・熱貫流熱量: Q = U・A・(t_i - t_o)  [W]
-・木根太補正: U = (1 - A_HB) U_main + A_HB U_HB</t>
+          <t>・熱抵抗: \(R = \frac{d}{\lambda}\)  [m²・K/W]
+・総合熱貫流抵抗: \(R_{\text{total}} = R_i + \sum \frac{d_k}{\lambda_k} + R_o + R_{\text{air}}\)
+・熱貫流率(熱通過率): \(U = \frac{1}{R_{\text{total}}}\)  [W/(m²・K)]
+・熱貫流熱量: \(Q = U \cdot A \cdot (t_i - t_o)\)  [W]
+・木根太補正: \(U = (1 - A_{\text{HB}}) U_{\text{main}} + A_{\text{HB}} U_{\text{HB}}\)</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -1042,10 +970,10 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>・直下照度: E_A = I / h²  [lx]
-・斜め照度: E_B = (I・cosθ) / r² = (I・cos³θ) / h²  [lx]
-・照度比: E_A / E_B = 1 / cos³θ = (1 + tan²θ)^(3/2)
-・平均照度(光束法): E = (N・F・U・M) / A  [lx]</t>
+          <t>・直下照度: \(E_A = \frac{I}{h^2}\)  [lx]
+・斜め照度: \(E_B = \frac{I \cdot \cos\theta}{r^2} = \frac{I \cdot \cos^3\theta}{h^2}\)  [lx]
+・照度比: \(\frac{E_A}{E_B} = \frac{1}{\cos^3\theta} = (1 + \tan^2\theta)^{3/2}\)
+・平均照度(光束法): \(E = \frac{N \cdot F \cdot U \cdot M}{A}\)  [lx]</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -1094,11 +1022,11 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>・必要換気量: Q = M / (C - C_0)  [m³/h]
-・温度差換気量: Q = αA √(2g h (t_i - t_o) / (273 + t_i))  [m³/s]
-・風力換気量: Q = αA・v √(C_1 - C_2)  [m³/s]
-・直列開口合成: 1/(αA)_total² = 1/(αA₁)² + 1/(αA₂)²
-・並列開口合成: (αA)_total = αA₁ + αA₂</t>
+          <t>・必要換気量: \(Q = \frac{M}{C - C_0}\)  [m³/h]
+・温度差換気量: \(Q = \alpha A \sqrt{\frac{2g h (t_i - t_o)}{273 + t_i}}\)  [m³/s]
+・風力換気量: \(Q = \alpha A \cdot v \sqrt{C_1 - C_2}\)  [m³/s]
+・直列開口合成: \(\frac{1}{(\alpha A)_{\text{total}}^2} = \frac{1}{(\alpha A_1)^2} + \frac{1}{(\alpha A_2)^2}\)
+・並列開口合成: \((\alpha A)_{\text{total}} = \alpha A_1 + \alpha A_2\)</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -1146,11 +1074,11 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>・顕熱負荷: q_s = ρ・c_p・Q・Δt / 3.6  [W]
-  (または Q_s = 1.2・Q_m³・Δt [kJ/h])
-・潜熱負荷: q_l = ρ・L・Q・Δx / 3.6  [W]
-・混合湯量: Q₁ t₁ + Q₂ t₂ = (Q₁ + Q₂) t_m
-・熱しゃく減量(%): (W_前 - W_後) / W_前 × 100</t>
+          <t>・顕熱負荷: \(q_s = \frac{\rho \cdot c_p \cdot Q \cdot \Delta t}{3.6}\)  [W]
+  (または \(Q_s = 1.2 \cdot Q_{m^3} \cdot \Delta t\) [kJ/h])
+・潜熱負荷: \(q_l = \frac{\rho \cdot L \cdot Q \cdot \Delta x}{3.6}\)  [W]
+・混合湯量: \(Q_1 t_1 + Q_2 t_2 = (Q_1 + Q_2) t_m\)
+・熱しゃく減量(%): \(\frac{W_{\text{前}} - W_{\text{後}}}{W_{\text{前}}} \times 100\%\)</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -1301,7 +1229,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>・C完全燃焼: C + O₂ → CO₂  (12g C に 1mol O₂)
+          <t>・C完全燃焼: C + O₂ → \(\text{CO}\)₂  (12g C に 1mol O₂)
 ・H完全燃焼: H₂ + 0.5 O₂ → H₂O  (2g H に 0.25mol O₂)
 ・S完全燃焼: S + O₂ → SO₂  (32g S に 1mol O₂)
 ・理論酸素量 O₀ = C/12 + H/4 + S/32 - O/32  [kmol/kg]
@@ -1398,7 +1326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1410,6 +1338,7 @@
     <col width="54" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1424,6 +1353,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
         <is>
@@ -1751,12 +1681,12 @@
       <c r="E14" s="19" t="inlineStr">
         <is>
           <t>・特定建築物: 延べ面積 3,000m² 以上(学校は 8,000m² 以上)。病院・店舗等含む。
-・空気環境基準: CO2 1,000 ppm以下 / CO 6 ppm以下(特例10ppm) / 浮遊粉塵 0.15 mg/m³以下 / 気流 0.5 m/s以下 / 温度 18~28℃ / 相対湿度 40~70% / ホルムアルデヒド 0.1 mg/m³(0.08ppm)以下。</t>
+・空気環境基準: \(\text{\(\text{CO}\)}_2\) 1,000 ppm以下 / \(\text{CO}\) 6 ppm以下(特例10ppm) / 浮遊粉塵 0.15 mg/m³以下 / 気流 0.5 m/s以下 / 温度 18~28℃ / 相対湿度 40~70% / ホルムアルデヒド 0.1 mg/m³(0.08ppm)以下。</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>★「CO基準は 100ppm 以下」は誤り(特例含め 6~10ppm 以下)。</t>
+          <t>★「\(\text{CO}\)基準は 100ppm 以下」は誤り(特例含め 6~10ppm 以下)。</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
@@ -1810,7 +1740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1822,6 +1752,7 @@
     <col width="53" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1832,10 +1763,11 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>水質指標(BOD/COD/SS/DO/TOC)、高度処理(A2O/MBR)、活性汚泥法、浄化槽法、環境基準・水濁法</t>
-        </is>
-      </c>
-    </row>
+          <t>水質指標(BOD/\(\text{CO}\)D/SS/DO/TOC)、高度処理(A2O/MBR)、活性汚泥法、浄化槽法、環境基準・水濁法</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
         <is>
@@ -1881,19 +1813,19 @@
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
-          <t>BOD / COD / SS / DO / TOC / 透過度 / 大腸菌数</t>
+          <t>BOD / \(\text{CO}\)D / SS / DO / TOC / 透過度 / 大腸菌数</t>
         </is>
       </c>
       <c r="E6" s="19" t="inlineStr">
         <is>
           <t>・BOD: 好気性微生物が有機物分解で消費する酸素量(20℃, 5日間培養)。
-・COD: 過マンガン酸カリウム等の酸化剤による酸素要求量(河川はBOD、湖沼・海域はCOD)。
+・\(\text{CO}\)D: 過マンガン酸カリウム等の酸化剤による酸素要求量(河川はBOD、湖沼・海域は\(\text{CO}\)D)。
 ・大腸菌数: 特定酵素基質寒天培地(37℃, 24時間培養)、単位 CFU/100mL (R4環境基準改定)。</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>★「河川の生活環境項目基準はCODである」は誤り(河川はBOD、湖沼・海域がCOD)。</t>
+          <t>★「河川の生活環境項目基準は\(\text{CO}\)Dである」は誤り(河川はBOD、湖沼・海域が\(\text{CO}\)D)。</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -1954,8 +1886,8 @@
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
-          <t>・硝化反応: NH₄⁺ + 2O₂ → NO₃⁻ + H₂O + 2H⁺ (好気性・独立栄養菌、pH低下・アルカリ度消費)。
-・脱窒反応: 2NO₃⁻ + 10[H] → N₂↑ + 2OH⁻ + 4H₂O (無酸素・通性嫌気菌、有機物/メタノール要求、pH上昇)。</t>
+          <t>・硝化反応: \(\text{NH}_4^+ + 2\text{O}_2 \rightarrow \text{NO}_3^- + \text{H}_2\text{O} + 2\text{H}^+\) (好気性・独立栄養菌、pH低下・アルカリ度消費)。
+・脱窒反応: \(2\text{NO}_3^- + 10[\text{H}] \rightarrow \text{N}_2\uparrow + 2\text{OH}^- + 4\text{H}_2\text{O}\) (無酸素・通性嫌気菌、有機物/メタノール要求、pH上昇)。</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
@@ -2022,7 +1954,7 @@
       <c r="E10" s="19" t="inlineStr">
         <is>
           <t>・健康項目: カドミウム、全シアン、鉛、PCB等(全国達成率 99% 以上)。
-・生活環境項目: BOD、COD、SS、DO、全窒素、全リン等。
+・生活環境項目: BOD、\(\text{CO}\)D、SS、DO、全窒素、全リン等。
 ・都道府県は条例で「上乗せ排水基準」を設定可能。
 ・東京湾・伊勢湾・瀬戸内海等は「総量削減規制」指定水域。</t>
         </is>
@@ -2083,7 +2015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2095,6 +2027,7 @@
     <col width="51" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -2109,6 +2042,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
         <is>
@@ -2292,7 +2226,7 @@
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
-          <t>三成分 / 高位・低位発熱量 / 熱しゃく減量 / サーマルNOx</t>
+          <t>三成分 / 高位・低位発熱量 / 熱しゃく減量 / サーマル\(\text{NO}_x\)</t>
         </is>
       </c>
       <c r="E10" s="19" t="inlineStr">
@@ -2300,12 +2234,12 @@
           <t>・ごみ三成分: 水分、可燃分、灰分 (%)
 ・低位発熱量 LHV: 高位発熱量 HHV から水蒸気潜熱分を差し引いた実効発熱量(炉設計に使用)。
 ・熱しゃく減量: 焼却残渣を 600℃ で強熱燃焼させた重量減少率(維持管理目標 5% 以下)。
-・焼却温度: 通常 800~900℃。700℃以上で悪臭分解、950℃超で灰溶融・炉壁付着、1000~1300℃超でThermal NOx急増。</t>
+・焼却温度: 通常 800~900℃。700℃以上で悪臭分解、950℃超で灰溶融・炉壁付着、1000~1300℃超でThermal \(\text{NO}_x\)急増。</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>★「Thermal NOxは750℃以下で急増する」は誤り(1000~1300℃以上の高温で生成)。</t>
+          <t>★「Thermal \(\text{NO}_x\)は750℃以下で急増する」は誤り(1000~1300℃以上の高温で生成)。</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -2394,7 +2328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I565"/>
+  <dimension ref="A1:I565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2408,6 +2342,7 @@
     <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -2422,6 +2357,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
         <is>
@@ -2799,7 +2735,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>低温冷風空調、VAV制御、躯体蓄熱、冷却水下限温度制御および冷凍機COPの正誤判定</t>
+          <t>低温冷風空調、VAV制御、躯体蓄熱、冷却水下限温度制御および冷凍機\(\text{CO}\)Pの正誤判定</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
@@ -2875,7 +2811,7 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>雨水利用初期カット、水道直結増圧給水、さや管ヘッダ工法、スプリンクラー予作動式およびCO2排出正誤判定</t>
+          <t>雨水利用初期カット、水道直結増圧給水、さや管ヘッダ工法、スプリンクラー予作動式および\(\text{\(\text{CO}\)}_2\)排出正誤判定</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr"/>
@@ -3619,7 +3555,7 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>基幹的設備改良マニュアルに基づくCO2削減対策、蒸気条件変更、対象発電電力量およびタービン変更の正誤判定</t>
+          <t>基幹的設備改良マニュアルに基づく\(\text{\(\text{CO}\)}_2\)削減対策、蒸気条件変更、対象発電電力量およびタービン変更の正誤判定</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
@@ -3879,7 +3815,7 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>換気計算（風力/温度差/CO2収支）</t>
+          <t>換気計算（風力/温度差/\(\text{\(\text{CO}\)}_2\)収支）</t>
         </is>
       </c>
       <c r="G43" s="13" t="n">
@@ -4087,7 +4023,7 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>全熱交換器バイパス、蓄熱槽システム、太陽電池（単結晶/多結晶）およびヒートポンプCOPの正誤判定</t>
+          <t>全熱交換器バイパス、蓄熱槽システム、太陽電池（単結晶/多結晶）およびヒートポンプ\(\text{CO}\)Pの正誤判定</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr"/>
@@ -4435,7 +4371,7 @@
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>建築物ライフサイクルCO2評価、フロンガス、ヒートアイランド現象および都市気候特性の正誤判定</t>
+          <t>建築物ライフサイクル\(\text{\(\text{CO}\)}_2\)評価、フロンガス、ヒートアイランド現象および都市気候特性の正誤判定</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr"/>
@@ -4899,7 +4835,7 @@
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>一般廃棄物処理施設の技術上の基準（燃焼温度800℃、集じん器入口200℃、CO連続測定）の正誤判定</t>
+          <t>一般廃棄物処理施設の技術上の基準（燃焼温度800℃、集じん器入口200℃、\(\text{CO}\)連続測定）の正誤判定</t>
         </is>
       </c>
       <c r="I69" s="14" t="inlineStr">
@@ -4979,7 +4915,7 @@
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>ごみ焼却施設の基幹的設備改良（CO2削減量評価対象、蒸気条件変更、復水器変更）の正誤判定</t>
+          <t>ごみ焼却施設の基幹的設備改良（\(\text{\(\text{CO}\)}_2\)削減量評価対象、蒸気条件変更、復水器変更）の正誤判定</t>
         </is>
       </c>
       <c r="I71" s="14" t="inlineStr">
@@ -6003,7 +5939,7 @@
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>BOD/COD環境基準達成率</t>
+          <t>BOD/\(\text{CO}\)D環境基準達成率</t>
         </is>
       </c>
       <c r="G98" s="13" t="n">
@@ -7327,7 +7263,7 @@
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>BOD/COD環境基準達成率</t>
+          <t>BOD/\(\text{CO}\)D環境基準達成率</t>
         </is>
       </c>
       <c r="G133" s="13" t="n">
@@ -9339,7 +9275,7 @@
       </c>
       <c r="F186" s="10" t="inlineStr">
         <is>
-          <t>換気計算（風力/温度差/CO2収支）</t>
+          <t>換気計算（風力/温度差/\(\text{\(\text{CO}\)}_2\)収支）</t>
         </is>
       </c>
       <c r="G186" s="13" t="n">
@@ -9503,7 +9439,7 @@
       </c>
       <c r="H190" s="10" t="inlineStr">
         <is>
-          <t>建築基準法必要換気量(20m3/h・人)、風による換気力、CO2発生量、第3種換気甲/乙種および平均空気齢定義の正誤判定</t>
+          <t>建築基準法必要換気量(20m3/h・人)、風による換気力、\(\text{\(\text{CO}\)}_2\)発生量、第3種換気甲/乙種および平均空気齢定義の正誤判定</t>
         </is>
       </c>
       <c r="I190" s="14" t="inlineStr">
@@ -9543,7 +9479,7 @@
       </c>
       <c r="H191" s="7" t="inlineStr">
         <is>
-          <t>水冷式/空冷式COP比較、吸収冷凍機（水/臭化リチウム）、ターボ冷凍機、吸収冷凍メリットおよびレシプロ冷凍機の正誤判定</t>
+          <t>水冷式/空冷式\(\text{CO}\)P比較、吸収冷凍機（水/臭化リチウム）、ターボ冷凍機、吸収冷凍メリットおよびレシプロ冷凍機の正誤判定</t>
         </is>
       </c>
       <c r="I191" s="14" t="inlineStr">
@@ -9743,7 +9679,7 @@
       </c>
       <c r="H196" s="10" t="inlineStr">
         <is>
-          <t>コージェネレーション定義（廃熱ボイラ誤記述）、環境会計、BEMS機能、LCCO2およびESCO事業の正誤判定</t>
+          <t>コージェネレーション定義（廃熱ボイラ誤記述）、環境会計、BEMS機能、LC\(\text{\(\text{CO}\)}_2\)およびES\(\text{CO}\)事業の正誤判定</t>
         </is>
       </c>
       <c r="I196" s="10" t="inlineStr"/>
@@ -9851,7 +9787,7 @@
       </c>
       <c r="F199" s="7" t="inlineStr">
         <is>
-          <t>BOD/COD環境基準達成率</t>
+          <t>BOD/\(\text{CO}\)D環境基準達成率</t>
         </is>
       </c>
       <c r="G199" s="13" t="n">
@@ -9859,7 +9795,7 @@
       </c>
       <c r="H199" s="7" t="inlineStr">
         <is>
-          <t>平成25年度公共用水域における水質環境基準（BOD/COD）達成率順位（河川 &gt; 海域 &gt; 湖沼）の判定</t>
+          <t>平成25年度公共用水域における水質環境基準（BOD/\(\text{CO}\)D）達成率順位（河川 &gt; 海域 &gt; 湖沼）の判定</t>
         </is>
       </c>
       <c r="I199" s="14" t="inlineStr">
@@ -10059,7 +9995,7 @@
       </c>
       <c r="H204" s="10" t="inlineStr">
         <is>
-          <t>透視度、DO、COD、大腸菌群（通性嫌気性菌誤り記述）およびMLSS定義に関する正誤判定</t>
+          <t>透視度、DO、\(\text{CO}\)D、大腸菌群（通性嫌気性菌誤り記述）およびMLSS定義に関する正誤判定</t>
         </is>
       </c>
       <c r="I204" s="14" t="inlineStr">
@@ -10547,7 +10483,7 @@
       </c>
       <c r="F217" s="7" t="inlineStr">
         <is>
-          <t>換気計算（風力/温度差/CO2収支）</t>
+          <t>換気計算（風力/温度差/\(\text{\(\text{CO}\)}_2\)収支）</t>
         </is>
       </c>
       <c r="G217" s="13" t="n">
@@ -10783,7 +10719,7 @@
       </c>
       <c r="F223" s="7" t="inlineStr">
         <is>
-          <t>換気計算（風力/温度差/CO2収支）</t>
+          <t>換気計算（風力/温度差/\(\text{\(\text{CO}\)}_2\)収支）</t>
         </is>
       </c>
       <c r="G223" s="13" t="n">
@@ -10831,7 +10767,7 @@
       </c>
       <c r="H224" s="10" t="inlineStr">
         <is>
-          <t>モリエル（p-h）線図における圧縮式冷凍サイクルの各過程（圧縮・蒸発）識別と成績係数（COP）算定式</t>
+          <t>モリエル（p-h）線図における圧縮式冷凍サイクルの各過程（圧縮・蒸発）識別と成績係数（\(\text{CO}\)P）算定式</t>
         </is>
       </c>
       <c r="I224" s="14" t="inlineStr">
@@ -11059,7 +10995,7 @@
       </c>
       <c r="H230" s="10" t="inlineStr">
         <is>
-          <t>在郷軍人会劇症肺炎（レジオネラ属菌）、シックハウス症候群、TVOC目標値、COヘモグロビン親和力およびクロルピリホスの正誤判定</t>
+          <t>在郷軍人会劇症肺炎（レジオネラ属菌）、シックハウス症候群、TVOC目標値、\(\text{CO}\)ヘモグロビン親和力およびクロルピリホスの正誤判定</t>
         </is>
       </c>
       <c r="I230" s="10" t="inlineStr"/>
@@ -11135,7 +11071,7 @@
       </c>
       <c r="H232" s="10" t="inlineStr">
         <is>
-          <t>空気清浄機清浄原理（衝突粘着式、静電式、活性炭吸着法（CO除去不可）、吸収法、ろ過式）の特徴比較</t>
+          <t>空気清浄機清浄原理（衝突粘着式、静電式、活性炭吸着法（\(\text{CO}\)除去不可）、吸収法、ろ過式）の特徴比較</t>
         </is>
       </c>
       <c r="I232" s="14" t="inlineStr">
@@ -11215,7 +11151,7 @@
       </c>
       <c r="H234" s="10" t="inlineStr">
         <is>
-          <t>化学的酸素要求量（COD）測定条件、短時間性、過マンガン酸カリウム酸化剤および硝酸性窒素の非検出性正誤判定</t>
+          <t>化学的酸素要求量（\(\text{CO}\)D）測定条件、短時間性、過マンガン酸カリウム酸化剤および硝酸性窒素の非検出性正誤判定</t>
         </is>
       </c>
       <c r="I234" s="14" t="inlineStr">
@@ -11599,7 +11535,7 @@
       </c>
       <c r="H244" s="10" t="inlineStr">
         <is>
-          <t>一般廃棄物焼却施設の技術上の基準（燃焼温度800℃以上・滞留2秒以上、一酸化炭素CO連続測定記録義務）の正誤判定</t>
+          <t>一般廃棄物焼却施設の技術上の基準（燃焼温度800℃以上・滞留2秒以上、一酸化炭素\(\text{CO}\)連続測定記録義務）の正誤判定</t>
         </is>
       </c>
       <c r="I244" s="14" t="inlineStr">
@@ -12179,7 +12115,7 @@
       </c>
       <c r="H259" s="7" t="inlineStr">
         <is>
-          <t>風力換気力、平均空気齢・平均滞留時間の定義、建築基準法換気基準（20m3/h・人）、CO2発生量および第一種〜第三種換気分類に関する正誤判定</t>
+          <t>風力換気力、平均空気齢・平均滞留時間の定義、建築基準法換気基準（20m3/h・人）、\(\text{\(\text{CO}\)}_2\)発生量および第一種〜第三種換気分類に関する正誤判定</t>
         </is>
       </c>
       <c r="I259" s="14" t="inlineStr">
@@ -12443,7 +12379,7 @@
       </c>
       <c r="F266" s="10" t="inlineStr">
         <is>
-          <t>換気計算（風力/温度差/CO2収支）</t>
+          <t>換気計算（風力/温度差/\(\text{\(\text{CO}\)}_2\)収支）</t>
         </is>
       </c>
       <c r="G266" s="13" t="n">
@@ -12451,7 +12387,7 @@
       </c>
       <c r="H266" s="10" t="inlineStr">
         <is>
-          <t>学校環境衛生基準（CO2濃度1,500ppm以下、外気400ppm、児童発生量11L/h・人）に基づく児童30人必要換気量計算</t>
+          <t>学校環境衛生基準（\(\text{\(\text{CO}\)}_2\)濃度1,500ppm以下、外気400ppm、児童発生量11L/h・人）に基づく児童30人必要換気量計算</t>
         </is>
       </c>
       <c r="I266" s="14" t="inlineStr">
@@ -13483,7 +13419,7 @@
       </c>
       <c r="H293" s="7" t="inlineStr">
         <is>
-          <t>省エネルギー設備（全熱交換器バイパス、蓄熱槽システム、コージェネレーション、太陽電池、COP定義）</t>
+          <t>省エネルギー設備（全熱交換器バイパス、蓄熱槽システム、コージェネレーション、太陽電池、\(\text{CO}\)P定義）</t>
         </is>
       </c>
       <c r="I293" s="7" t="inlineStr"/>
@@ -14011,7 +13947,7 @@
       </c>
       <c r="H307" s="7" t="inlineStr">
         <is>
-          <t>生活環境項目と適用水域の組合せ（BOD-湖沼、COD-海域、pH-河川、大腸菌群数-湖沼、DO-海域）</t>
+          <t>生活環境項目と適用水域の組合せ（BOD-湖沼、\(\text{CO}\)D-海域、pH-河川、大腸菌群数-湖沼、DO-海域）</t>
         </is>
       </c>
       <c r="I307" s="7" t="inlineStr"/>
@@ -14235,7 +14171,7 @@
       </c>
       <c r="H313" s="7" t="inlineStr">
         <is>
-          <t>廃棄物焼却温度（燃焼室内温度800〜900℃、ダイオキシン抑熱800℃以上、溶融950℃超、悪臭分解700℃以上、Thermal NOx 1000〜1300℃超）</t>
+          <t>廃棄物焼却温度（燃焼室内温度800〜900℃、ダイオキシン抑熱800℃以上、溶融950℃超、悪臭分解700℃以上、Thermal \(\text{NO}_x\) 1000〜1300℃超）</t>
         </is>
       </c>
       <c r="I313" s="14" t="inlineStr">
@@ -15031,7 +14967,7 @@
       </c>
       <c r="F334" s="10" t="inlineStr">
         <is>
-          <t>換気計算（風力/温度差/CO2収支）</t>
+          <t>換気計算（風力/温度差/\(\text{\(\text{CO}\)}_2\)収支）</t>
         </is>
       </c>
       <c r="G334" s="13" t="n">
@@ -15039,7 +14975,7 @@
       </c>
       <c r="H334" s="10" t="inlineStr">
         <is>
-          <t>在室者数・一人当たりCO2発生量・内外CO2濃度差に基づく機械換気回数の定型計算</t>
+          <t>在室者数・一人当たり\(\text{\(\text{CO}\)}_2\)発生量・内外\(\text{\(\text{CO}\)}_2\)濃度差に基づく機械換気回数の定型計算</t>
         </is>
       </c>
       <c r="I334" s="14" t="inlineStr">
@@ -15375,7 +15311,7 @@
       </c>
       <c r="H343" s="7" t="inlineStr">
         <is>
-          <t>水質汚濁防止法に基づく一律排水基準項目（SS, COD, BOD, pH）と除外項目の正誤判定</t>
+          <t>水質汚濁防止法に基づく一律排水基準項目（SS, \(\text{CO}\)D, BOD, pH）と除外項目の正誤判定</t>
         </is>
       </c>
       <c r="I343" s="7" t="inlineStr"/>
@@ -15595,7 +15531,7 @@
       </c>
       <c r="H349" s="7" t="inlineStr">
         <is>
-          <t>ごみ焼却排ガス中のNOx生成要因（Thermal/Fuel）、バグフィルターおよび塩化水素除去の正誤判定</t>
+          <t>ごみ焼却排ガス中の\(\text{NO}_x\)生成要因（Thermal/Fuel）、バグフィルターおよび塩化水素除去の正誤判定</t>
         </is>
       </c>
       <c r="I349" s="7" t="inlineStr"/>
@@ -16059,7 +15995,7 @@
       </c>
       <c r="H361" s="7" t="inlineStr">
         <is>
-          <t>定常状態における汚染物質濃度式、環境衛生基準数値（CO2, ホルムアルデヒド, CO）および必要換気量基準に関する正誤判定</t>
+          <t>定常状態における汚染物質濃度式、環境衛生基準数値（\(\text{\(\text{CO}\)}_2\), ホルムアルデヒド, \(\text{CO}\)）および必要換気量基準に関する正誤判定</t>
         </is>
       </c>
       <c r="I361" s="14" t="inlineStr">
@@ -16407,7 +16343,7 @@
       </c>
       <c r="H370" s="10" t="inlineStr">
         <is>
-          <t>室容積・換気回数・在室人数および1人当たりCO2発生量に基づく室内CO2濃度の計算</t>
+          <t>室容積・換気回数・在室人数および1人当たり\(\text{\(\text{CO}\)}_2\)発生量に基づく室内\(\text{\(\text{CO}\)}_2\)濃度の計算</t>
         </is>
       </c>
       <c r="I370" s="14" t="inlineStr">
@@ -16519,7 +16455,7 @@
       </c>
       <c r="H373" s="7" t="inlineStr">
         <is>
-          <t>学校環境衛生基準における浮遊粉塵（0.10mg/m³）、CO2（1,500ppm）、温度、相対湿度および気流基準に関する正誤判定</t>
+          <t>学校環境衛生基準における浮遊粉塵（0.10mg/m³）、\(\text{\(\text{CO}\)}_2\)（1,500ppm）、温度、相対湿度および気流基準に関する正誤判定</t>
         </is>
       </c>
       <c r="I373" s="14" t="inlineStr">
@@ -16635,7 +16571,7 @@
       </c>
       <c r="H376" s="10" t="inlineStr">
         <is>
-          <t>粒状活性炭処理におけるCOD、リン酸イオン、色度、臭気およびSSの除去対象に関する正誤判定</t>
+          <t>粒状活性炭処理における\(\text{CO}\)D、リン酸イオン、色度、臭気およびSSの除去対象に関する正誤判定</t>
         </is>
       </c>
       <c r="I376" s="14" t="inlineStr">
@@ -16667,7 +16603,7 @@
       </c>
       <c r="F377" s="7" t="inlineStr">
         <is>
-          <t>BOD/COD環境基準達成率</t>
+          <t>BOD/\(\text{CO}\)D環境基準達成率</t>
         </is>
       </c>
       <c r="G377" s="13" t="n">
@@ -16675,7 +16611,7 @@
       </c>
       <c r="H377" s="7" t="inlineStr">
         <is>
-          <t>公共用水域における生活環境項目環境基準（BOD/COD）達成率の順位（河川＞海域＞湖沼）に関する正誤判定</t>
+          <t>公共用水域における生活環境項目環境基準（BOD/\(\text{CO}\)D）達成率の順位（河川＞海域＞湖沼）に関する正誤判定</t>
         </is>
       </c>
       <c r="I377" s="14" t="inlineStr">
@@ -17403,7 +17339,7 @@
       </c>
       <c r="H396" s="10" t="inlineStr">
         <is>
-          <t>日射の波長区分、散乱・天空放射、CO2による吸収、短波長・長波長透過性および実効放射に関する正誤判定</t>
+          <t>日射の波長区分、散乱・天空放射、\(\text{\(\text{CO}\)}_2\)による吸収、短波長・長波長透過性および実効放射に関する正誤判定</t>
         </is>
       </c>
       <c r="I396" s="10" t="inlineStr"/>
@@ -17775,7 +17711,7 @@
       </c>
       <c r="H406" s="10" t="inlineStr">
         <is>
-          <t>開放型石油ストーブからのCO発生量・室容積・換気回数条件における定常室内CO濃度の定型計算</t>
+          <t>開放型石油ストーブからの\(\text{CO}\)発生量・室容積・換気回数条件における定常室内\(\text{CO}\)濃度の定型計算</t>
         </is>
       </c>
       <c r="I406" s="14" t="inlineStr">
@@ -17999,7 +17935,7 @@
       </c>
       <c r="H412" s="10" t="inlineStr">
         <is>
-          <t>河川環境基準項目（BOD適用、CODは湖沼海域）、短時間測定、酸化剤種類、亜硝酸性窒素のCOD検出および測定条件依存性に関する正誤判定</t>
+          <t>河川環境基準項目（BOD適用、\(\text{CO}\)Dは湖沼海域）、短時間測定、酸化剤種類、亜硝酸性窒素の\(\text{CO}\)D検出および測定条件依存性に関する正誤判定</t>
         </is>
       </c>
       <c r="I412" s="10" t="inlineStr"/>
@@ -18915,7 +18851,7 @@
       </c>
       <c r="H436" s="10" t="inlineStr">
         <is>
-          <t>圧縮式冷凍機のモリエル線図における圧縮過程・蒸発過程および成績係数(COP)</t>
+          <t>圧縮式冷凍機のモリエル線図における圧縮過程・蒸発過程および成績係数(\(\text{CO}\)P)</t>
         </is>
       </c>
       <c r="I436" s="14" t="inlineStr">
@@ -19635,7 +19571,7 @@
       </c>
       <c r="H455" s="7" t="inlineStr">
         <is>
-          <t>焼却炉燃焼室温度(800〜900℃)、Thermal NOx(750℃以下生成)および融着</t>
+          <t>焼却炉燃焼室温度(800〜900℃)、Thermal \(\text{NO}_x\)(750℃以下生成)および融着</t>
         </is>
       </c>
       <c r="I455" s="14" t="inlineStr">
@@ -20011,7 +19947,7 @@
       </c>
       <c r="H465" s="7" t="inlineStr">
         <is>
-          <t>室内空気汚染（粉じん・CO2許容濃度・CO発生等）に関する記述</t>
+          <t>室内空気汚染（粉じん・\(\text{\(\text{CO}\)}_2\)許容濃度・\(\text{CO}\)発生等）に関する記述</t>
         </is>
       </c>
       <c r="I465" s="14" t="inlineStr">
@@ -20751,7 +20687,7 @@
       </c>
       <c r="H485" s="7" t="inlineStr">
         <is>
-          <t>水質指標（透視度・COD・SS・MLSS・大腸菌群）に関する記述</t>
+          <t>水質指標（透視度・\(\text{CO}\)D・SS・MLSS・大腸菌群）に関する記述</t>
         </is>
       </c>
       <c r="I485" s="14" t="inlineStr">
@@ -21707,7 +21643,7 @@
       </c>
       <c r="H510" s="10" t="inlineStr">
         <is>
-          <t>PM2.5環境基準、シックハウス指針値、TVOC暫定目標値およびCO2影響濃度</t>
+          <t>PM2.5環境基準、シックハウス指針値、TVOC暫定目標値および\(\text{\(\text{CO}\)}_2\)影響濃度</t>
         </is>
       </c>
       <c r="I510" s="14" t="inlineStr">
@@ -21747,7 +21683,7 @@
       </c>
       <c r="H511" s="7" t="inlineStr">
         <is>
-          <t>建築物衛生法における空気環境基準の数値（CO、CO2、温度、相対湿度、ホルムアルデヒド）</t>
+          <t>建築物衛生法における空気環境基準の数値（\(\text{CO}\)、\(\text{\(\text{CO}\)}_2\)、温度、相対湿度、ホルムアルデヒド）</t>
         </is>
       </c>
       <c r="I511" s="14" t="inlineStr">
@@ -22051,7 +21987,7 @@
       </c>
       <c r="H519" s="7" t="inlineStr">
         <is>
-          <t>JIS K 0102 酸性過マンガン酸カリウムによる酸素消費量（COD）操作法</t>
+          <t>JIS K 0102 酸性過マンガン酸カリウムによる酸素消費量（\(\text{CO}\)D）操作法</t>
         </is>
       </c>
       <c r="I519" s="14" t="inlineStr">
@@ -22167,7 +22103,7 @@
       </c>
       <c r="H522" s="10" t="inlineStr">
         <is>
-          <t>公共用水域における環境基準（BOD/COD）達成率の順位（河川・海域・湖沼）</t>
+          <t>公共用水域における環境基準（BOD/\(\text{CO}\)D）達成率の順位（河川・海域・湖沼）</t>
         </is>
       </c>
       <c r="I522" s="14" t="inlineStr">
@@ -22823,7 +22759,7 @@
       </c>
       <c r="F539" s="7" t="inlineStr">
         <is>
-          <t>換気計算（風力/温度差/CO2収支）</t>
+          <t>換気計算（風力/温度差/\(\text{\(\text{CO}\)}_2\)収支）</t>
         </is>
       </c>
       <c r="G539" s="13" t="n">
@@ -22907,7 +22843,7 @@
       </c>
       <c r="H541" s="7" t="inlineStr">
         <is>
-          <t>コジェネ部分負荷特性、BEMSとコミッショニング、エアフローウィンドウの目的、全熱交換器と外気冷房、CO2濃度による外気量制御</t>
+          <t>コジェネ部分負荷特性、BEMSとコミッショニング、エアフローウィンドウの目的、全熱交換器と外気冷房、\(\text{\(\text{CO}\)}_2\)濃度による外気量制御</t>
         </is>
       </c>
       <c r="I541" s="14" t="inlineStr">
@@ -23051,7 +22987,7 @@
       </c>
       <c r="F545" s="7" t="inlineStr">
         <is>
-          <t>換気計算（風力/温度差/CO2収支）</t>
+          <t>換気計算（風力/温度差/\(\text{\(\text{CO}\)}_2\)収支）</t>
         </is>
       </c>
       <c r="G545" s="13" t="n">
@@ -23287,7 +23223,7 @@
       </c>
       <c r="F551" s="7" t="inlineStr">
         <is>
-          <t>BOD/COD環境基準達成率</t>
+          <t>BOD/\(\text{CO}\)D環境基準達成率</t>
         </is>
       </c>
       <c r="G551" s="13" t="n">
@@ -23555,7 +23491,7 @@
       </c>
       <c r="H558" s="10" t="inlineStr">
         <is>
-          <t>廃棄物焼却温度（800〜900℃）、悪臭・有害物質分解温度（700℃以上）、サーマルNOx生成条件（1000〜1300℃以上の高温で急増、750℃以下では生成しにくい）、ダイオキシン抑制（800℃以上）、灰溶融温度（950℃超）</t>
+          <t>廃棄物焼却温度（800〜900℃）、悪臭・有害物質分解温度（700℃以上）、サーマル\(\text{NO}_x\)生成条件（1000〜1300℃以上の高温で急増、750℃以下では生成しにくい）、ダイオキシン抑制（800℃以上）、灰溶融温度（950℃超）</t>
         </is>
       </c>
       <c r="I558" s="14" t="inlineStr">
@@ -23827,1092 +23763,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="35" customHeight="1">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>【過去16年分網羅】衛生工学一次試験 出題歴のある環境基準値・数値ルール一覧</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="21" t="inlineStr">
-        <is>
-          <t>分類</t>
-        </is>
-      </c>
-      <c r="B3" s="21" t="inlineStr">
-        <is>
-          <t>項目・管理対象</t>
-        </is>
-      </c>
-      <c r="C3" s="21" t="inlineStr">
-        <is>
-          <t>規定値・基準値・単位</t>
-        </is>
-      </c>
-      <c r="D3" s="21" t="inlineStr">
-        <is>
-          <t>根拠法令・基準名</t>
-        </is>
-      </c>
-      <c r="E3" s="21" t="inlineStr">
-        <is>
-          <t>主な該当過去問</t>
-        </is>
-      </c>
-      <c r="F3" s="21" t="inlineStr">
-        <is>
-          <t>試験での引っかけパターン・重要メモ</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="22" t="inlineStr">
-        <is>
-          <t>室内空気質</t>
-        </is>
-      </c>
-      <c r="B4" s="23" t="inlineStr">
-        <is>
-          <t>二酸化炭素 (CO2) 濃度</t>
-        </is>
-      </c>
-      <c r="C4" s="24" t="inlineStr">
-        <is>
-          <t>1,000 ppm 以下 (0.1%)</t>
-        </is>
-      </c>
-      <c r="D4" s="23" t="inlineStr">
-        <is>
-          <t>建築物衛生法 / 建築基準法</t>
-        </is>
-      </c>
-      <c r="E4" s="25" t="inlineStr">
-        <is>
-          <t>H23, H26, H29, R1本, R3, R4, R6</t>
-        </is>
-      </c>
-      <c r="F4" s="23" t="inlineStr">
-        <is>
-          <t>労働衛生(作業環境)の管理目標は1,500 ppm。試験では10,000 ppm等の誤りで引っかけ出題あり。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
-        <is>
-          <t>室内空気質</t>
-        </is>
-      </c>
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>一酸化炭素 (CO) 濃度</t>
-        </is>
-      </c>
-      <c r="C5" s="28" t="inlineStr">
-        <is>
-          <t>6 ppm 以下 (特例10 ppm以下)</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="inlineStr">
-        <is>
-          <t>建築物衛生法施行令 (R4改定)</t>
-        </is>
-      </c>
-      <c r="E5" s="29" t="inlineStr">
-        <is>
-          <t>R4, R6等</t>
-        </is>
-      </c>
-      <c r="F5" s="27" t="inlineStr">
-        <is>
-          <t>令和4年4月改定により10ppm→6ppmに厳格化。旧基準(10ppm)や100ppm等の誤り記述に注意。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="22" t="inlineStr">
-        <is>
-          <t>室内空気質</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>浮遊粉じん量</t>
-        </is>
-      </c>
-      <c r="C6" s="24" t="inlineStr">
-        <is>
-          <t>0.15 mg/m³ 以下</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t>建築物衛生法</t>
-        </is>
-      </c>
-      <c r="E6" s="25" t="inlineStr">
-        <is>
-          <t>H23, H28, R1本, R3等</t>
-        </is>
-      </c>
-      <c r="F6" s="23" t="inlineStr">
-        <is>
-          <t>粒径10μm以下の粉じんが対象。1.5 mg/m³など桁違いの数値で出題。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
-        <is>
-          <t>室内空気質</t>
-        </is>
-      </c>
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>室内温度基準</t>
-        </is>
-      </c>
-      <c r="C7" s="28" t="inlineStr">
-        <is>
-          <t>18 ℃ 以上 28 ℃ 以下</t>
-        </is>
-      </c>
-      <c r="D7" s="27" t="inlineStr">
-        <is>
-          <t>建築物衛生法</t>
-        </is>
-      </c>
-      <c r="E7" s="29" t="inlineStr">
-        <is>
-          <t>H28, R1本, R3, R6</t>
-        </is>
-      </c>
-      <c r="F7" s="27" t="inlineStr">
-        <is>
-          <t>「17℃以上」や「15℃以上」などの不適切選択肢に注意。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
-        <is>
-          <t>室内空気質</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>室内相対湿度基準</t>
-        </is>
-      </c>
-      <c r="C8" s="24" t="inlineStr">
-        <is>
-          <t>40 % 以上 70 % 以下</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t>建築物衛生法</t>
-        </is>
-      </c>
-      <c r="E8" s="25" t="inlineStr">
-        <is>
-          <t>H23, H28, R1本, R3, R6</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>30%以上や80%以下などの範囲変更引っかけあり。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
-        <is>
-          <t>室内空気質</t>
-        </is>
-      </c>
-      <c r="B9" s="27" t="inlineStr">
-        <is>
-          <t>気流速度</t>
-        </is>
-      </c>
-      <c r="C9" s="28" t="inlineStr">
-        <is>
-          <t>0.5 m/s 以下</t>
-        </is>
-      </c>
-      <c r="D9" s="27" t="inlineStr">
-        <is>
-          <t>建築物衛生法</t>
-        </is>
-      </c>
-      <c r="E9" s="29" t="inlineStr">
-        <is>
-          <t>H23, H28, R1本, R3</t>
-        </is>
-      </c>
-      <c r="F9" s="27" t="inlineStr">
-        <is>
-          <t>ドラフト(不快気流)防止のため0.5m/s以下。1.0m/s等は誤り。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
-        <is>
-          <t>室内空気質</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>ホルムアルデヒド量</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="inlineStr">
-        <is>
-          <t>0.1 mg/m³ 以下 (0.08 ppm)</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>建築物衛生法 / 厚労省指針</t>
-        </is>
-      </c>
-      <c r="E10" s="25" t="inlineStr">
-        <is>
-          <t>R6等</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>シックハウス対策。カビ代謝物ではなく建材・接着剤からの放散VOC。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>室内空気質</t>
-        </is>
-      </c>
-      <c r="B11" s="27" t="inlineStr">
-        <is>
-          <t>TVOC (総揮発性有機化合物)</t>
-        </is>
-      </c>
-      <c r="C11" s="28" t="inlineStr">
-        <is>
-          <t>400 μg/m³ 以下</t>
-        </is>
-      </c>
-      <c r="D11" s="27" t="inlineStr">
-        <is>
-          <t>厚労省暫定目標値</t>
-        </is>
-      </c>
-      <c r="E11" s="29" t="inlineStr">
-        <is>
-          <t>R6等</t>
-        </is>
-      </c>
-      <c r="F11" s="27" t="inlineStr">
-        <is>
-          <t>400 mg/m³（桁違い）や必須法律義務（正しくは暫定目標値）の引っかけ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
-        <is>
-          <t>採光・シックハウス</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>有効採光窓面積比率 (教室)</t>
-        </is>
-      </c>
-      <c r="C12" s="24" t="inlineStr">
-        <is>
-          <t>1 / 5 以上</t>
-        </is>
-      </c>
-      <c r="D12" s="23" t="inlineStr">
-        <is>
-          <t>建築基準法第28条</t>
-        </is>
-      </c>
-      <c r="E12" s="25" t="inlineStr">
-        <is>
-          <t>R5等</t>
-        </is>
-      </c>
-      <c r="F12" s="23" t="inlineStr">
-        <is>
-          <t>住宅居室は 1/7 以上。教室・保育室は 1/5 以上。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
-        <is>
-          <t>採光・シックハウス</t>
-        </is>
-      </c>
-      <c r="B13" s="27" t="inlineStr">
-        <is>
-          <t>常時換気設備 (住宅居室)</t>
-        </is>
-      </c>
-      <c r="C13" s="28" t="inlineStr">
-        <is>
-          <t>0.5 回/h 以上</t>
-        </is>
-      </c>
-      <c r="D13" s="27" t="inlineStr">
-        <is>
-          <t>建築基準法</t>
-        </is>
-      </c>
-      <c r="E13" s="29" t="inlineStr">
-        <is>
-          <t>R7等</t>
-        </is>
-      </c>
-      <c r="F13" s="27" t="inlineStr">
-        <is>
-          <t>シックハウス対策として全居室に0.5回/hの機械換気設備設置が義務付け。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="22" t="inlineStr">
-        <is>
-          <t>給排水設備</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>給水管内流速</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>1.5 ～ 2.0 m/s 以下</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>給排水設備規程 (SHASE-S)</t>
-        </is>
-      </c>
-      <c r="E14" s="25" t="inlineStr">
-        <is>
-          <t>H23, R1本, R3, R5</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>ウォーターハンマーや管内侵食(エロージョン)防止のため2.0m/s以下。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>給排水設備</t>
-        </is>
-      </c>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>大便器洗浄弁 (フラッシュバルブ) 給水圧力</t>
-        </is>
-      </c>
-      <c r="C15" s="28" t="inlineStr">
-        <is>
-          <t>0.07 MPa (70 kPa) 以上</t>
-        </is>
-      </c>
-      <c r="D15" s="27" t="inlineStr">
-        <is>
-          <t>給排水設備規程</t>
-        </is>
-      </c>
-      <c r="E15" s="29" t="inlineStr">
-        <is>
-          <t>R4, R5等</t>
-        </is>
-      </c>
-      <c r="F15" s="27" t="inlineStr">
-        <is>
-          <t>最低必要圧力ゲージ圧で70kPa。ロータンクは30kPa以上。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="22" t="inlineStr">
-        <is>
-          <t>給排水設備</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>排水トラップ 封水深</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
-        <is>
-          <t>50 mm 以上 100 mm 以下</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>建築基準法 / SHASE-S</t>
-        </is>
-      </c>
-      <c r="E16" s="25" t="inlineStr">
-        <is>
-          <t>H23, H28, R1本, R3, R4</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>50mm未満は破封しやすく、100mm超は自浄作用低下・排水障害。最大封水深50mmは誤り(正しくは上限100mm)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="26" t="inlineStr">
-        <is>
-          <t>給排水設備</t>
-        </is>
-      </c>
-      <c r="B17" s="27" t="inlineStr">
-        <is>
-          <t>貯水槽 (受水槽) 保守空間</t>
-        </is>
-      </c>
-      <c r="C17" s="28" t="inlineStr">
-        <is>
-          <t>面・下部: 0.6m以上 / 上部: 1.0m以上</t>
-        </is>
-      </c>
-      <c r="D17" s="27" t="inlineStr">
-        <is>
-          <t>建築物衛生法</t>
-        </is>
-      </c>
-      <c r="E17" s="29" t="inlineStr">
-        <is>
-          <t>R3, R4, R5, R7</t>
-        </is>
-      </c>
-      <c r="F17" s="27" t="inlineStr">
-        <is>
-          <t>上下側面すべて30cm/60cm等にする引っかけ。上部は1.0m以上確保。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="22" t="inlineStr">
-        <is>
-          <t>給排水設備</t>
-        </is>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>受水槽有効容量</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>1日予想給水量の 1/2 (4/10～6/10)</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="inlineStr">
-        <is>
-          <t>給排水設備規程</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="inlineStr">
-        <is>
-          <t>R1本, R7</t>
-        </is>
-      </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>高置水槽は1日給水量の1/10〜1/5(約1〜2時間分)。受水槽は1/2程度。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="26" t="inlineStr">
-        <is>
-          <t>水質環境基準</t>
-        </is>
-      </c>
-      <c r="B19" s="27" t="inlineStr">
-        <is>
-          <t>水質健康項目 (カドミウム・シアン等)</t>
-        </is>
-      </c>
-      <c r="C19" s="28" t="inlineStr">
-        <is>
-          <t>27項目 (原則年平均値または検出されないこと)</t>
-        </is>
-      </c>
-      <c r="D19" s="27" t="inlineStr">
-        <is>
-          <t>環境基本法</t>
-        </is>
-      </c>
-      <c r="E19" s="29" t="inlineStr">
-        <is>
-          <t>H23, R3, R5, R7</t>
-        </is>
-      </c>
-      <c r="F19" s="27" t="inlineStr">
-        <is>
-          <t>達成率は例年99%以上。全シアン・総水銀等は年平均値ではなく最高値/不検出基準。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="22" t="inlineStr">
-        <is>
-          <t>水質環境基準</t>
-        </is>
-      </c>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>河川の有機汚濁指標</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="inlineStr">
-        <is>
-          <t>BOD (生物化学的酸素要求量)</t>
-        </is>
-      </c>
-      <c r="D20" s="23" t="inlineStr">
-        <is>
-          <t>環境基本法 生活環境項目</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="inlineStr">
-        <is>
-          <t>H23, R3, R5, R7</t>
-        </is>
-      </c>
-      <c r="F20" s="23" t="inlineStr">
-        <is>
-          <t>河川はBOD。湖沼および海域はCODが指標（河川にCODは誤り）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="26" t="inlineStr">
-        <is>
-          <t>水質環境基準</t>
-        </is>
-      </c>
-      <c r="B21" s="27" t="inlineStr">
-        <is>
-          <t>湖沼・海域の有機汚濁指標</t>
-        </is>
-      </c>
-      <c r="C21" s="28" t="inlineStr">
-        <is>
-          <t>COD (化学的酸素要求量)</t>
-        </is>
-      </c>
-      <c r="D21" s="27" t="inlineStr">
-        <is>
-          <t>環境基本法 生活環境項目</t>
-        </is>
-      </c>
-      <c r="E21" s="29" t="inlineStr">
-        <is>
-          <t>H23, R3, R5, R7</t>
-        </is>
-      </c>
-      <c r="F21" s="27" t="inlineStr">
-        <is>
-          <t>富栄養化対策として全窒素・全リン基準も適用。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="22" t="inlineStr">
-        <is>
-          <t>水質環境基準</t>
-        </is>
-      </c>
-      <c r="B22" s="23" t="inlineStr">
-        <is>
-          <t>大腸菌数 (生活環境項目)</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="inlineStr">
-        <is>
-          <t>特定酵素基質寒天培地 / 37℃ 24時間</t>
-        </is>
-      </c>
-      <c r="D22" s="23" t="inlineStr">
-        <is>
-          <t>環境基準 (R4改定)</t>
-        </is>
-      </c>
-      <c r="E22" s="25" t="inlineStr">
-        <is>
-          <t>R4, R5, R7</t>
-        </is>
-      </c>
-      <c r="F22" s="23" t="inlineStr">
-        <is>
-          <t>令和4年度より「大腸菌群数」から「大腸菌数(CFU/100mL)」へ改定。コロニー形状識別は誤り(色で識別)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="26" t="inlineStr">
-        <is>
-          <t>下水・浄化槽</t>
-        </is>
-      </c>
-      <c r="B23" s="27" t="inlineStr">
-        <is>
-          <t>合併処理浄化槽 放流BOD基準</t>
-        </is>
-      </c>
-      <c r="C23" s="28" t="inlineStr">
-        <is>
-          <t>20 mg/L 以下 (BOD除去率 90% 以上)</t>
-        </is>
-      </c>
-      <c r="D23" s="27" t="inlineStr">
-        <is>
-          <t>浄化槽法 / 構造基準</t>
-        </is>
-      </c>
-      <c r="E23" s="29" t="inlineStr">
-        <is>
-          <t>R1本, R3, R5, R7</t>
-        </is>
-      </c>
-      <c r="F23" s="27" t="inlineStr">
-        <is>
-          <t>単独処理浄化槽は新設禁止。放流BOD 20mg/L以下、BOD除去率90%以上。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="22" t="inlineStr">
-        <is>
-          <t>下水・浄化槽</t>
-        </is>
-      </c>
-      <c r="B24" s="23" t="inlineStr">
-        <is>
-          <t>浄化槽 保守点検記録保存期間</t>
-        </is>
-      </c>
-      <c r="C24" s="24" t="inlineStr">
-        <is>
-          <t>3 年間</t>
-        </is>
-      </c>
-      <c r="D24" s="23" t="inlineStr">
-        <is>
-          <t>浄化槽法</t>
-        </is>
-      </c>
-      <c r="E24" s="25" t="inlineStr">
-        <is>
-          <t>R7等</t>
-        </is>
-      </c>
-      <c r="F24" s="23" t="inlineStr">
-        <is>
-          <t>マニフェスト(5年)との数字混同引っかけに注意。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="26" t="inlineStr">
-        <is>
-          <t>水質試験</t>
-        </is>
-      </c>
-      <c r="B25" s="27" t="inlineStr">
-        <is>
-          <t>BOD5 測定条件</t>
-        </is>
-      </c>
-      <c r="C25" s="28" t="inlineStr">
-        <is>
-          <t>20 ℃ ・ 5 日間 暗所培養</t>
-        </is>
-      </c>
-      <c r="D25" s="27" t="inlineStr">
-        <is>
-          <t>JIS K 0102</t>
-        </is>
-      </c>
-      <c r="E25" s="29" t="inlineStr">
-        <is>
-          <t>R1本, R3, R4</t>
-        </is>
-      </c>
-      <c r="F25" s="27" t="inlineStr">
-        <is>
-          <t>培養温度30℃や7日間にする引っかけ。正しくは20℃・5日間。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="22" t="inlineStr">
-        <is>
-          <t>ごみ焼却炉</t>
-        </is>
-      </c>
-      <c r="B26" s="23" t="inlineStr">
-        <is>
-          <t>燃焼室内保持温度</t>
-        </is>
-      </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>800 ～ 900 ℃</t>
-        </is>
-      </c>
-      <c r="D26" s="23" t="inlineStr">
-        <is>
-          <t>ごみ焼却施設維持管理指針</t>
-        </is>
-      </c>
-      <c r="E26" s="25" t="inlineStr">
-        <is>
-          <t>R3, R4, R6, R7</t>
-        </is>
-      </c>
-      <c r="F26" s="23" t="inlineStr">
-        <is>
-          <t>悪臭・有害ガス(700℃以上で分解)やダイオキシン類(800℃以上)を抑制。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="26" t="inlineStr">
-        <is>
-          <t>ごみ焼却炉</t>
-        </is>
-      </c>
-      <c r="B27" s="27" t="inlineStr">
-        <is>
-          <t>ダイオキシン類 抑制条件</t>
-        </is>
-      </c>
-      <c r="C27" s="28" t="inlineStr">
-        <is>
-          <t>800 ℃ 以上 / 滞留時間 2秒 以上</t>
-        </is>
-      </c>
-      <c r="D27" s="27" t="inlineStr">
-        <is>
-          <t>ダイオキシン類対策特別措置法</t>
-        </is>
-      </c>
-      <c r="E27" s="29" t="inlineStr">
-        <is>
-          <t>R3, R4, R6, R7</t>
-        </is>
-      </c>
-      <c r="F27" s="27" t="inlineStr">
-        <is>
-          <t>排ガス冷却過程(200〜300℃)の急速冷却でデノボ合成を防止。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="22" t="inlineStr">
-        <is>
-          <t>ごみ焼却炉</t>
-        </is>
-      </c>
-      <c r="B28" s="23" t="inlineStr">
-        <is>
-          <t>熱しゃく減量 (焼却残さ維持管理目標)</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="inlineStr">
-        <is>
-          <t>5 % 以下</t>
-        </is>
-      </c>
-      <c r="D28" s="23" t="inlineStr">
-        <is>
-          <t>ごみ焼却施設維持管理指針</t>
-        </is>
-      </c>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>R3, R7</t>
-        </is>
-      </c>
-      <c r="F28" s="23" t="inlineStr">
-        <is>
-          <t>未燃分割合を示す。目標値「20%以上」等の誤り記述で出題。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="26" t="inlineStr">
-        <is>
-          <t>ごみ焼却炉</t>
-        </is>
-      </c>
-      <c r="B29" s="27" t="inlineStr">
-        <is>
-          <t>Thermal NOx 生成温度</t>
-        </is>
-      </c>
-      <c r="C29" s="28" t="inlineStr">
-        <is>
-          <t>1,000 ～ 1,300 ℃ 以上で急増</t>
-        </is>
-      </c>
-      <c r="D29" s="27" t="inlineStr">
-        <is>
-          <t>大気汚染防止法</t>
-        </is>
-      </c>
-      <c r="E29" s="29" t="inlineStr">
-        <is>
-          <t>R4, R6, R7</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="inlineStr">
-        <is>
-          <t>「750℃以下でThermal NOxが生成する」は誤り(高温で生成)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="22" t="inlineStr">
-        <is>
-          <t>ごみ焼却炉</t>
-        </is>
-      </c>
-      <c r="B30" s="23" t="inlineStr">
-        <is>
-          <t>焼却灰 溶融温度</t>
-        </is>
-      </c>
-      <c r="C30" s="24" t="inlineStr">
-        <is>
-          <t>950 ℃ 超</t>
-        </is>
-      </c>
-      <c r="D30" s="23" t="inlineStr">
-        <is>
-          <t>プラント維持管理</t>
-        </is>
-      </c>
-      <c r="E30" s="25" t="inlineStr">
-        <is>
-          <t>R4, R6, R7</t>
-        </is>
-      </c>
-      <c r="F30" s="23" t="inlineStr">
-        <is>
-          <t>950℃を超えるとクリンカ(灰溶融物)が炉壁に付着。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="26" t="inlineStr">
-        <is>
-          <t>廃棄物法規</t>
-        </is>
-      </c>
-      <c r="B31" s="27" t="inlineStr">
-        <is>
-          <t>産業廃棄物マニフェスト保存期間</t>
-        </is>
-      </c>
-      <c r="C31" s="28" t="inlineStr">
-        <is>
-          <t>5 年間</t>
-        </is>
-      </c>
-      <c r="D31" s="27" t="inlineStr">
-        <is>
-          <t>廃棄物処理法</t>
-        </is>
-      </c>
-      <c r="E31" s="29" t="inlineStr">
-        <is>
-          <t>H23, H28, R1本, R3, R4, R7</t>
-        </is>
-      </c>
-      <c r="F31" s="27" t="inlineStr">
-        <is>
-          <t>E票(最終処分完了報告)受領後、5年間保存義務。紙・電子共通。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="22" t="inlineStr">
-        <is>
-          <t>廃棄物法規</t>
-        </is>
-      </c>
-      <c r="B32" s="23" t="inlineStr">
-        <is>
-          <t>特別管理産業廃棄物 (液性基準)</t>
-        </is>
-      </c>
-      <c r="C32" s="24" t="inlineStr">
-        <is>
-          <t>強酸: pH 2.0以下 / 強アルカリ: pH 12.5以上</t>
-        </is>
-      </c>
-      <c r="D32" s="23" t="inlineStr">
-        <is>
-          <t>廃棄物処理法</t>
-        </is>
-      </c>
-      <c r="E32" s="25" t="inlineStr">
-        <is>
-          <t>R3, R5等</t>
-        </is>
-      </c>
-      <c r="F32" s="23" t="inlineStr">
-        <is>
-          <t>引火性廃油(引火点70℃未満)なども該当。管理者設置は義務。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="26" t="inlineStr">
-        <is>
-          <t>最終処分場</t>
-        </is>
-      </c>
-      <c r="B33" s="27" t="inlineStr">
-        <is>
-          <t>遮水工保護砂層厚さ</t>
-        </is>
-      </c>
-      <c r="C33" s="28" t="inlineStr">
-        <is>
-          <t>50 cm 以上</t>
-        </is>
-      </c>
-      <c r="D33" s="27" t="inlineStr">
-        <is>
-          <t>最終処分場構造基準</t>
-        </is>
-      </c>
-      <c r="E33" s="29" t="inlineStr">
-        <is>
-          <t>R7等</t>
-        </is>
-      </c>
-      <c r="F33" s="27" t="inlineStr">
-        <is>
-          <t>遮水シート損傷防止のため砂等を50cm以上敷設。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="22" t="inlineStr">
-        <is>
-          <t>最終処分場</t>
-        </is>
-      </c>
-      <c r="B34" s="23" t="inlineStr">
-        <is>
-          <t>地下水観測井 設置数</t>
-        </is>
-      </c>
-      <c r="C34" s="24" t="inlineStr">
-        <is>
-          <t>2 か所以上</t>
-        </is>
-      </c>
-      <c r="D34" s="23" t="inlineStr">
-        <is>
-          <t>最終処分場維持管理基準</t>
-        </is>
-      </c>
-      <c r="E34" s="25" t="inlineStr">
-        <is>
-          <t>R7等</t>
-        </is>
-      </c>
-      <c r="F34" s="23" t="inlineStr">
-        <is>
-          <t>周縁に上流・下流含め2か所以上設置して地下水質検査。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="26" t="inlineStr">
-        <is>
-          <t>最終処分場</t>
-        </is>
-      </c>
-      <c r="B35" s="27" t="inlineStr">
-        <is>
-          <t>跡地開口部閉鎖覆土厚さ</t>
-        </is>
-      </c>
-      <c r="C35" s="28" t="inlineStr">
-        <is>
-          <t>50 cm 以上 (一般・管理型)</t>
-        </is>
-      </c>
-      <c r="D35" s="27" t="inlineStr">
-        <is>
-          <t>最終処分場廃止基準</t>
-        </is>
-      </c>
-      <c r="E35" s="29" t="inlineStr">
-        <is>
-          <t>R4等</t>
-        </is>
-      </c>
-      <c r="F35" s="27" t="inlineStr">
-        <is>
-          <t>「1m以上の土砂及び遮水シートで閉鎖」は誤り。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>